--- a/System_development/magnet_design/A650-88/A650_BillofMaterials.xlsx
+++ b/System_development/magnet_design/A650-88/A650_BillofMaterials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usman\OneDrive - Georgia Southern University\Desktop\USC-1stSemester\NMR\Compact-NMR\System_development\magnet_design\A645_Tesla_magnet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mk103\Documents\GitHub\Compact-NMR\System_development\magnet_design\A650-88\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A76EBBD-3AF9-4816-B2AD-07400A096807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C50A7F-F6D8-4E9E-B147-5E2F666BEA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BillofMaterials" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>BILL OF MATERIALS</t>
   </si>
@@ -123,6 +123,21 @@
   </si>
   <si>
     <t>https://www.grainger.com/product/1ZAH9?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=702409156c4ad209c3e5d4ab8dbeaccacf86bcc7bd495f2916140c14c90db510&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item</t>
+  </si>
+  <si>
+    <t>DIN Rail</t>
+  </si>
+  <si>
+    <t>Aluminum, 35 mm Wd, 1 m Lg</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/18Z758?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=ac232cc7b935c7736f4435c50323bb59f2921ffb94961f879b251578be9b251d&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item</t>
+  </si>
+  <si>
+    <t>0.75 in Thick, 12 in x 24 in, Opaque</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/1ZAJ5?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=cff7e1848fea8b130032e724c132e8345d3df8293bda65d2d5c96015c86769b3&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item</t>
   </si>
 </sst>
 </file>
@@ -1017,22 +1032,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
     <col min="6" max="6" width="39" customWidth="1"/>
-    <col min="7" max="7" width="47.109375" customWidth="1"/>
+    <col min="7" max="7" width="47.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1061,7 +1076,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1082,7 +1097,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1103,7 +1118,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1123,7 +1138,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1144,7 +1159,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1164,7 +1179,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1184,7 +1199,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1204,31 +1219,65 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>11.21</v>
+      </c>
+      <c r="E10" s="4">
+        <v>11.21</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>46.3</v>
+      </c>
+      <c r="E11" s="4">
+        <v>46.3</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D12" s="3"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D14" s="3"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D18" s="3"/>
     </row>
   </sheetData>
@@ -1240,6 +1289,8 @@
     <hyperlink ref="F7" r:id="rId4" xr:uid="{F0F72660-1ACA-4E4A-9485-D726524E371A}"/>
     <hyperlink ref="F8" r:id="rId5" xr:uid="{C00EA188-A35F-4C4D-BF7E-4D0578E6B0B0}"/>
     <hyperlink ref="F9" r:id="rId6" xr:uid="{E9C17141-238C-4F6E-9CD3-5A272872E047}"/>
+    <hyperlink ref="F10" r:id="rId7" xr:uid="{9E5E6868-8C71-4C8A-A71E-7EA67D58D6E9}"/>
+    <hyperlink ref="F11" r:id="rId8" xr:uid="{BC911DDC-578B-4366-B22E-849A11967B3D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
